--- a/doc/tickets/CJS_journey_ownership.xlsx
+++ b/doc/tickets/CJS_journey_ownership.xlsx
@@ -10,6 +10,7 @@
     <sheet name="By journey" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="All observations" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Framework changes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Handler code" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All observations'!$A$1:$H$173</definedName>
@@ -55,7 +56,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +103,11 @@
         <fgColor rgb="00EFF3F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6DDE1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -120,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,6 +174,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,14 +707,23 @@
       <c r="L5" s="8" t="inlineStr">
         <is>
           <t>2. Applicant details not aligned - should be row wise
+     -&gt; Studio &gt; Design tab. Place the applicant fields on one row of the 12-column grid (ZRAK_CJ_LAY).
 4. Permit / EID / trade licence order wrong, no search button
+     -&gt; Field order in the Design tab; the search button appears when the field's FTYPE is SEARCH.
 5. Company details field order not correct
+     -&gt; Design tab.
 7. Grid: all row fields mandatory, drop the delete1 column
+     -&gt; REQUIRED per field, and remove the column from the grid spec in ZRAK_T_JNY_FLD-DEFAULT_VAL.
 8. Units and No. of Months should be dropdowns
+     -&gt; Add the values to ZRAK_T_JNY_OPT and set CLOSED_LIST = X.
 9. Supplier company: order and mandatory indicators
+     -&gt; Design tab + REQUIRED.
 10. Step name 'Letter from the Supplier Company' -&gt; 'Documents'
+     -&gt; Already coded in ZRAK_CJ_FIXPACK, English and Arabic. Run the report for this journey.
 11. Mandatory attachment labels need the * indicator
-12. Declaration &amp; Notes missing</t>
+     -&gt; The engine draws the asterisk now - RENDER_ATTACH( ) passes the native required property. What is left is ticking REQUIRED on each upload field.
+12. Declaration &amp; Notes missing
+     -&gt; Add a DISPLAY field whose DEFAULT_VAL is TEXT:@nnn pointing at a ZRAK_T_CJ_TXT row, so it reads in both languages.</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -711,8 +735,11 @@
       <c r="N5" s="5" t="inlineStr">
         <is>
           <t>1. Initial page loads with error messages
+     -&gt; The screenshot is already on the ticket, but Jira is not reachable from where this register is built - paste the error text here. Most likely the required-field messages firing before the citizen has typed anything, which is a rule/required config question, not the engine.
 3. EPDA permit no &amp; applicant type data missing
-14. Case created (1959717) but attachments not saved</t>
+     -&gt; The handler has no ON_INIT, so nothing seeds these. Confirm the field names in ZRAK_T_JNY_FLD and an ON_INIT can be written in an hour.
+14. Case created (1959717) but attachments not saved
+     -&gt; Instrumented: ZCL_RAK_JOURNEY_BE now counts the files it could not read, says so on screen and names them on the trace. Re-run with &amp;trace=x and send the ATTACH line.</t>
         </is>
       </c>
     </row>
@@ -764,22 +791,32 @@
       <c r="K6" s="9" t="inlineStr">
         <is>
           <t>ZCL_EPDA_E022_DEV_PROJ_LOGIC
-FIX WRITTEN, IN GIT - YOURS TO TAKE:
+CODE READY - see the 'Handler code' sheet:
 3. Applicant details are duplicated</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
           <t>2. Applicant details not aligned - should be row wise
+     -&gt; Design tab.
 4. Emirates ID search should follow the format; Browse not required
+     -&gt; PLACEHOLDER for the mask, REGEX for the format, FTYPE SEARCH instead of the browse control.
 5. Permit / EID / trade licence order; permit number not a dropdown
+     -&gt; Design tab + FTYPE.
 6. Company details field order not correct
+     -&gt; Design tab.
 7. Company name English &amp; Arabic duplicated
+     -&gt; Two fields are bound to the same value. Hide one in ZRAK_T_JNY_FLD.
 8. Rename step 'Development Project' -&gt; 'Project Details'
+     -&gt; Coded in ZRAK_CJ_FIXPACK, EN + AR.
 9. Rename step 'Trade license' -&gt; 'Documents'
+     -&gt; Coded in ZRAK_CJ_FIXPACK, EN + AR.
 10. Trade licence attachment is missing
+     -&gt; Add the upload field to the Documents step.
 11. Declaration &amp; Note missing
-12. Step 5 request confirmation not required</t>
+     -&gt; DISPLAY field with a TEXT: default.
+12. Step 5 request confirmation not required
+     -&gt; Coded in ZRAK_CJ_FIXPACK as STEP_OFF - reversible, sets ACTIVE blank.</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
@@ -790,7 +827,9 @@
       <c r="N6" s="5" t="inlineStr">
         <is>
           <t>1. Initial page loads with error messages
-14. Attachments are not saving</t>
+     -&gt; The screenshot is on the ticket; paste it here - Jira is not reachable from where this register is built.
+14. Attachments are not saving
+     -&gt; Re-run with &amp;trace=x and send the ATTACH line.</t>
         </is>
       </c>
     </row>
@@ -914,19 +953,27 @@
       <c r="K8" s="9" t="inlineStr">
         <is>
           <t>ZCL_E017_NOC_EXP_CHEM_LOGIC
-FIX WRITTEN, IN GIT - YOURS TO TAKE:
+CODE READY - see the 'Handler code' sheet:
+2. Representative + owner EID search errors and will not move to the next step
 4. Add Chemical - all fields should be mandatory</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
           <t>1. Owner search should be in EID format; Browse not required
+     -&gt; PLACEHOLDER + REGEX; FTYPE SEARCH. Listed in the fixpack worklist.
 3. Permit number / trade licence etc. not required on the chemical tab
+     -&gt; Coded in ZRAK_CJ_FIXPACK as three HIDE rules anchored on the CHEMICALS_DETAILS grid.
 8. 'Use a previous declaration' field not required
+     -&gt; Hide the field.
 9. HS code should be a guided formatted number with a watermark
+     -&gt; REGEX for the format, PLACEHOLDER for the watermark.
 12. 'up to 2 MB' repeats on every attachment; mandatory indicator missing
+     -&gt; The asterisk is engine-side and done; the repeated size hint is per-field wording.
 13. Preview page should be removed
-14. Step 5 request confirmation not required</t>
+     -&gt; Coded in ZRAK_CJ_FIXPACK as STEP_OFF.
+14. Step 5 request confirmation not required
+     -&gt; Coded in ZRAK_CJ_FIXPACK as STEP_OFF.</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -937,11 +984,14 @@
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>2. Representative + owner EID search errors and will not move to the next step
-7. Bill of Lading input clears its own value
+          <t>7. Bill of Lading input clears its own value
+     -&gt; Check BOL_POP actually exists in ZRAK_T_JNY_FLD - a field name that is not on the journey accepts set_val and get_val and does nothing.
 10. Modify - existing values are not showing
+     -&gt; The edit path does not load the row back into the dialog. Needs a run.
 11. Search from History is missing
-16. Attachments are not saving</t>
+     -&gt; A real gap, not a bug: the legacy control reads ChemicalHistorySet on zega_fw_fnd_srv and no CJS class calls it. Needs a decision before it can be built.
+16. Attachments are not saving
+     -&gt; Re-run with &amp;trace=x.</t>
         </is>
       </c>
     </row>
@@ -998,7 +1048,9 @@
       <c r="L9" s="8" t="inlineStr">
         <is>
           <t>6. Arabic translation not complete
-11. Mandatory attachments need the *</t>
+     -&gt; Handed to anand on the thread. ZLABEL_AR across the journey.
+11. Mandatory attachments need the *
+     -&gt; Engine draws it; tick REQUIRED on each upload field.</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1157,7 +1209,9 @@
       <c r="N11" s="5" t="inlineStr">
         <is>
           <t>1. The service does not work on the portal screen
-11. Cannot post payment through the landing page</t>
+     -&gt; Check which handler class the journey row points at first - two classes claim D014.
+11. Cannot post payment through the landing page
+     -&gt; Run with &amp;trace=x: PREPARE_PAYMENT( ) names its exit - NOCASE, NOSCREEN or NOURL - which says whether the case, the screen mapping or the gateway address is missing.</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1268,9 @@
       <c r="L12" s="8" t="inlineStr">
         <is>
           <t>1. Owner - BP labels missing
-5. Mandatory attachments need the *</t>
+     -&gt; Fill ZLABEL / ZLABEL_AR. In the fixpack worklist.
+5. Mandatory attachments need the *
+     -&gt; Tick REQUIRED on each upload field.</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1282,7 +1338,8 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t>1. Field should read Distance, not Educational stage</t>
+          <t>1. Field should read Distance, not Educational stage
+     -&gt; ZLABEL / ZLABEL_AR. In the fixpack worklist - the field name is not known from here.</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1350,7 +1407,8 @@
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>2. Mandatory attachments need the *</t>
+          <t>2. Mandatory attachments need the *
+     -&gt; Tick REQUIRED on each upload field.</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
@@ -1417,7 +1475,8 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>3. Mandatory attachments need the *</t>
+          <t>3. Mandatory attachments need the *
+     -&gt; Tick REQUIRED on each upload field.</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1482,7 +1541,8 @@
       <c r="K16" s="9" t="inlineStr">
         <is>
           <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC
-FIX WRITTEN, IN GIT - YOURS TO TAKE:
+CODE READY - see the 'Handler code' sheet:
+2. Representative + owner EID search errors and will not move on
 4. Add Chemical - all fields should be mandatory
 10. Backend POST failed - CX_SY_CONVERSION_NO_NUMBER, cannot go to the next step</t>
         </is>
@@ -1490,9 +1550,13 @@
       <c r="L16" s="8" t="inlineStr">
         <is>
           <t>1. Owner search should be in EID format; Browse not required
+     -&gt; PLACEHOLDER + REGEX; FTYPE SEARCH. In the fixpack worklist.
 3. Permit number / trade licence etc. not required on the chemical tab
+     -&gt; Coded in ZRAK_CJ_FIXPACK as three HIDE rules.
 8. 'Use a previous declaration' field not required
-9. HS code should be a guided formatted number with a watermark</t>
+     -&gt; Hide the field.
+9. HS code should be a guided formatted number with a watermark
+     -&gt; REGEX + PLACEHOLDER.</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
@@ -1502,8 +1566,8 @@
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>2. Representative + owner EID search errors and will not move on
-7. Bill of Lading input clears its own value</t>
+          <t>7. Bill of Lading input clears its own value
+     -&gt; Check BOL_POP exists in ZRAK_T_JNY_FLD.</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1623,8 @@
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
-          <t>2. Mandatory attachments need the *</t>
+          <t>2. Mandatory attachments need the *
+     -&gt; Tick REQUIRED on each upload field.</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1637,7 +1702,9 @@
       <c r="N18" s="5" t="inlineStr">
         <is>
           <t>4. The payment step errors when paying
-5. Cannot complete the case at the payment step</t>
+     -&gt; Run with &amp;trace=x. PREPARE_PAYMENT( ) reports its exit and the keys the backend answered with, which separates 'no case' from 'no gateway address'.
+5. Cannot complete the case at the payment step
+     -&gt; Blocker - same run as above.</t>
         </is>
       </c>
     </row>
@@ -1694,21 +1761,37 @@
       <c r="L19" s="8" t="inlineStr">
         <is>
           <t>2. Applicant details not aligned - should be row wise
+     -&gt; Design tab.
 3. Applicant details are duplicated
+     -&gt; Not the same cause as E022 - this handler writes nothing. Two fields are bound to the same value; hide one.
 4. Emirates ID search should follow the format; Browse not required
+     -&gt; PLACEHOLDER + REGEX; FTYPE SEARCH.
 5. Permit / EID / trade licence order; permit number not a dropdown
+     -&gt; Design tab + FTYPE.
 6. Company details field order not correct
+     -&gt; Design tab.
 7. Company name English &amp; Arabic duplicated
+     -&gt; Hide one of the two fields.
 8. 'Material Text 1' should read 'Name'
+     -&gt; ZLABEL / ZLABEL_AR.
 9. Issuing emirates should be a dropdown
+     -&gt; ZRAK_T_JNY_OPT + CLOSED_LIST.
 10. Vehicle Code must not allow more than 2 digits
+     -&gt; MAX_LEN on the field.
 11. Vehicle Plate must not allow more than 4 digits
+     -&gt; MAX_LEN on the field.
 12. Remove the 'Mtable Delete 2' column
+     -&gt; Drop it from the grid spec in DEFAULT_VAL.
 13. Units should be a dropdown
+     -&gt; ZRAK_T_JNY_OPT + CLOSED_LIST.
 14. Address, Registered Emirate, Trade Licence should be inputs, not display
+     -&gt; Change FTYPE from DISPLAY to INPUT and tick REQUIRED.
 15. Step name should change to Documents
+     -&gt; Step title, EN + AR.
 16. Mandatory attachments need the *
-17. Declaration &amp; Notes missing</t>
+     -&gt; Tick REQUIRED on each upload field.
+17. Declaration &amp; Notes missing
+     -&gt; DISPLAY field with a TEXT: default.</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -1722,7 +1805,9 @@
       <c r="N19" s="5" t="inlineStr">
         <is>
           <t>1. Initial page loads with error messages
-19. Attachments are not saving</t>
+     -&gt; The screenshot is on the ticket; paste it here - Jira is not reachable from where this register is built.
+19. Attachments are not saving
+     -&gt; Re-run with &amp;trace=x.</t>
         </is>
       </c>
     </row>
@@ -1779,15 +1864,25 @@
       <c r="L20" s="8" t="inlineStr">
         <is>
           <t>2. Applicant details not aligned - should be row wise
+     -&gt; Design tab.
 3. Applicant details are duplicated
+     -&gt; Two fields bound to the same value; hide one.
 4. Emirates ID search should follow the format; Browse not required
+     -&gt; PLACEHOLDER + REGEX; FTYPE SEARCH.
 5. Permit / EID / trade licence order; permit number not a dropdown
+     -&gt; Design tab + FTYPE.
 6. Rename the step 'Material Origin source' to 'Batteries/Scrap Details'
+     -&gt; Step title, EN + AR.
 7. Fields under Material origin source must be dynamic and mandatory by dropdown value
+     -&gt; Show/hide belongs in ZRAK_T_JNY_RULE keyed on the dropdown, with REQUIRED on the fields it reveals.
 8. Vehicle code 1 digit, vehicle plate 4 digits
+     -&gt; MAX_LEN on both fields.
 9. 'Materials Det' is duplicated and should be renamed
+     -&gt; Hide one, rename the other.
 10. Declaration &amp; Note missing
-11. Step 5 request confirmation not required</t>
+     -&gt; DISPLAY field with a TEXT: default.
+11. Step 5 request confirmation not required
+     -&gt; STEP_OFF - the fixpack does this for other journeys and takes one more line.</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
@@ -1798,7 +1893,9 @@
       <c r="N20" s="5" t="inlineStr">
         <is>
           <t>1. Initial page loads with error messages
-13. Attachments are not saving</t>
+     -&gt; The screenshot is on the ticket; paste it here - Jira is not reachable from where this register is built.
+13. Attachments are not saving
+     -&gt; Re-run with &amp;trace=x.</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1951,8 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>1. CJS service Not found</t>
+          <t>1. CJS service Not found
+     -&gt; The handler class exists and is complete. Check the ZRAK_T_JNY row and the launch URL's journey id - a code that does not resolve gives exactly this.</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
@@ -1916,16 +2014,20 @@
       <c r="K22" s="9" t="inlineStr">
         <is>
           <t>ZCL_E025_BEEKEEPING_LOGIC
-FIX WRITTEN, IN GIT - YOURS TO TAKE:
+CODE READY - see the 'Handler code' sheet:
 6. Applicant BP not saved in the record model, not in the backend application</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
           <t>1. Emirates ID search should follow the format; Browse not required
+     -&gt; PLACEHOLDER + REGEX; FTYPE SEARCH.
 2. Number of Apiaries max 2 digits; Expected Production max 6
+     -&gt; MAX_LEN on both fields.
 3. Mandatory attachments need the *
-4. Declaration &amp; Note missing</t>
+     -&gt; Tick REQUIRED on each upload field.
+4. Declaration &amp; Note missing
+     -&gt; DISPLAY field with a TEXT: default.</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
@@ -1935,7 +2037,8 @@
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>5. Case id is not correct - shows the wrong number</t>
+          <t>5. Case id is not correct - shows the wrong number
+     -&gt; Send the number that was shown next to the case it belongs to. On some families the journey key is not the case id, and the engine has one resolver for that - but it needs the pair to confirm.</t>
         </is>
       </c>
     </row>
@@ -1987,15 +2090,18 @@
       <c r="K23" s="9" t="inlineStr">
         <is>
           <t>ZCL_E026_TREE_REMOVAL_LOGIC
-FIX WRITTEN, IN GIT - YOURS TO TAKE:
+CODE READY - see the 'Handler code' sheet:
 5. Applicant BP not saved in the record model, not in the backend application</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
           <t>1. Emirates ID search should follow the format; Browse not required
+     -&gt; PLACEHOLDER + REGEX; FTYPE SEARCH.
 2. Mandatory attachments need the *
-3. Declaration &amp; Note missing</t>
+     -&gt; Tick REQUIRED on each upload field.
+3. Declaration &amp; Note missing
+     -&gt; DISPLAY field with a TEXT: default.</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
@@ -2005,7 +2111,8 @@
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t>4. Case id is not correct - shows the wrong number</t>
+          <t>4. Case id is not correct - shows the wrong number
+     -&gt; Same as E025 - send the pair of numbers.</t>
         </is>
       </c>
     </row>
@@ -3699,19 +3806,19 @@
           <t>Representative + owner EID search errors and will not move to the next step</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>Reporter + developer</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>Needs a look</t>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>Journey developer - ABAP</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>Handler class - developer</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>Needs one run with the exact search value. The popup validation now blocks correctly, so an error here is the search itself.</t>
+          <t>Fix written - see the Handler code sheet. ON_CUSTOM_VALIDATE refused step 0 whenever APPLICANT_ROLE was set and its projected flags PARTNER_OWNER / PARTNER_REP were not. Those flags are only written by ON_CHANGE, so a BP search coming back left the pair inconsistent, and re-selecting the same value raises no CHANGE - so the one instruction the message gave could not clear it. It re-derives now instead of refusing.</t>
         </is>
       </c>
     </row>
@@ -6339,19 +6446,19 @@
           <t>Representative + owner EID search errors and will not move on</t>
         </is>
       </c>
-      <c r="F108" s="10" t="inlineStr">
-        <is>
-          <t>Reporter + developer</t>
-        </is>
-      </c>
-      <c r="G108" s="10" t="inlineStr">
-        <is>
-          <t>Needs a look</t>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>Journey developer - ABAP</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>Handler class - developer</t>
         </is>
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>Re-test after the class is activated.</t>
+          <t>Same fix as E017 - ON_CUSTOM_VALIDATE re-derives the role flags instead of refusing the step. Re-test after the class is activated, since it had no active version.</t>
         </is>
       </c>
     </row>
@@ -8967,12 +9074,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9002,58 +9110,78 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Applies to</t>
+          <t>What else it touches</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Risk</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>ZCL_RAK_JOURNEY_LOGIC</t>
+          <t>ZCL_RAK_JOURNEY_ENGINE + ZCL_RAK_JOURNEY_RENDER</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Popup dialogs draw their own messages instead of putting them behind the modal, and lay out in two columns (FormContainers, not the columnsL property).</t>
+          <t>NAV_LOCKED( ): once a PAYFEE field on any step holds PAID, or the journey is submitted or closed, Back / the stepper dots / the tab strip stop offering a way back, and the event handler refuses the move even where something was still drawn.</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>every journey</t>
+          <t>EVERY journey with a fee, in every family - the twelve Municipality journeys that carry RAKPAY included - and every journey at all once it is submitted.</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>HIGH - a real behaviour change and not opt-in. If any service must let the citizen go back after paying, say so before this is pulled.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>ZCL_RAK_JOURNEY_RENDER</t>
+          <t>ZCL_RAK_JOURNEY_BE</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>A 'Not now' button beside Send feedback, so feedback is no longer compulsory; attachment labels carry the native required property, so the * actually draws.</t>
+          <t>A backend read now SEEDS an editable grid and does not RE-seed one that already holds rows - the citizen's copy wins. GET_BACKEND_TABLE( ) still returns the backend's current answer, so grids served from the store are untouched.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>every journey</t>
+          <t>Any family with an editable grid fed by a backend read. Store-fed grids - the LICENSES lists on D003/D004/D011 - are not affected.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>MEDIUM - stated cost: a grid the backend re-derives from an EARLIER step's answer no longer refreshes when that answer changes. A handler that needs it to clears the grid itself from ON_CHANGE( ).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>ZCL_RAK_JOURNEY_ENGINE</t>
+          <t>ZCL_RAK_JOURNEY_RENDER + ZCL_RAK_JOURNEY_ENGINE</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>FBSKIP handling behind the 'Not now' button.</t>
+          <t>A 'Not now' button beside Send feedback, and FBSKIP behind it, so the closing page always has a way out.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>every journey</t>
+          <t>Every journey whose WANTS_FEEDBACK( ) is true - that is the base default, so all of them unless a handler says otherwise.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>MEDIUM - feedback becomes skippable everywhere. Deliberate: before this the page had no other exit. If a service must have compulsory feedback, decide now.</t>
         </is>
       </c>
     </row>
@@ -9065,63 +9193,885 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Counts the attachments it could not read, says so on screen and names them on the trace - so 'attachments not saving' can be diagnosed in one run.</t>
+          <t>A staged file whose content the store cannot return is counted, named on the trace and reported once on screen as a Warning instead of vanishing.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>every journey</t>
+          <t>Every journey - but the code only runs when a file is already being lost.</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>LOW - inert unless the fault is happening. Adds nothing to a healthy submit.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>ZIF_RAK_JOURNEY</t>
+          <t>ZCL_RAK_JOURNEY_RENDER</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>MSGS( ) so a dialog can read the pending messages.</t>
+          <t>RENDER_ATTACH( ) passes the native REQUIRED property on the attachment label, so the asterisk actually draws. The old CSS-class marker never reached the DOM.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>every journey</t>
+          <t>Every journey with an upload field already marked REQUIRED in ZRAK_T_JNY_FLD.</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>LOW - visual only, and it follows configuration that is already there. Enforcement was already correct; only the marker was missing.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>ZRAK_CJ_FIXPACK</t>
+          <t>ZCL_RAK_JOURNEY_LOGIC</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Report. Applies 19 of the config points mechanically, per journey, idempotent.</t>
+          <t>DIALOG_FORM( ) repeats the pending messages inside the dialog, so a handler that refuses an OK and keeps the dialog open can be read.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>run it per journey</t>
+          <t>Every popup built through DIALOG_FORM( ) - D001, D004, D006, E016-E018, showcase, test.</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>LOW - draws nothing when there are no pending messages, so a dialog that opens clean looks exactly as it did.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>ZCL_RAK_JOURNEY_LOGIC</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>DIALOG_FORM( ) gained IV_COLUMNS for two- and three-column dialogs.</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Nothing unless a handler asks for it. IV_COLUMNS DEFAULT 1 draws the identical markup the method always drew; only E016/E017/E018 pass 2.</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>NONE - opt-in per call site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ZIF_RAK_JOURNEY</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>MSGS( ) added so a dialog can read the pending messages.</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>The interface is implemented by ZCL_RAK_JOURNEY_ENGINE and by nothing else, so no other class has to implement anything.</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>NONE - additive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ZRAK_CJ_FIXPACK</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>New report. Applies 19 of the config points mechanically, per journey, idempotent.</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Only the journey named on its selection screen.</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>NONE - new object, nothing calls it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>ZRAK_CJ_BACKUP</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Report. Full export and import of one journey's configuration - the fallback before anyone edits config in anger.</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>run it per journey</t>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>New report. Full export and import of one journey's configuration - the fallback before anyone edits config in anger.</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Only the journey named on its selection screen.</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>NONE - new object, nothing calls it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="120" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Handler class fixes - the code, to retype in SE24</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>These are the journey's OWN class, not the framework. Read it, take it or write your own - it is your service. Where a whole method is given, it is the complete current method: replace the method body with it. Nothing here is pushed for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Journey</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Method / where</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>What it fixes</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>E025</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-703</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E025_BEEKEEPING_LOGIC</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>see the code</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Applicant BP was written to the owner SEARCH field and then blanked</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>* --- private section: the constant named the wrong field ------------
+*   was:  constants C_LOGIN_BP type STRING value 'OWNER_BP' ##NO_TEXT.
+  constants C_LOGIN_BP type STRING value 'LOGIN_BP' ##NO_TEXT.
+* --- ZIF_RAK_JOURNEY_LOGIC~ON_INIT, last line inside the IF -----------
+*   was:  io_ctx-&gt;set_val( iv_name = 'OWNER_BP' iv_value = ' ' ).
+*   'OWNER_BP' is the owner search box (see ON_SEARCH), not the applicant.
+  io_ctx-&gt;set_val( iv_name = c_owner_bp iv_value = ' ' ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>E026</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-704</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E026_TREE_REMOVAL_LOGIC</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>see the code</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Applicant BP never reached LOGIN_BP</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>* --- private section: add, leave C_LOGIN_BP exactly as it is ---------
+  constants C_APP_BP type STRING value 'LOGIN_BP' ##NO_TEXT.
+* --- ZIF_RAK_JOURNEY_LOGIC~ON_INIT, straight after the existing line --
+    io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).
+    io_ctx-&gt;set_val( iv_name = c_app_bp   iv_value = |{ lv_loginbp }| ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>E018</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-697</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>see the code</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>The class had NO ACTIVE VERSION - a string constant does not take an empty literal, so every earlier fix was in the source and none of it was running</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>* --- private section --------------------------------------------------
+*   was:  constants C_IMPEXP type STRING value ''.       &lt;- will not compile
+  constants C_IMPEXP type STRING value IS INITIAL ##NO_TEXT.
+* Activate the class after this and re-test the whole journey - including the
+* CX_SY_CONVERSION_NO_NUMBER on post, which may go with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="150" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>E022</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-684</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_EPDA_E022_DEV_PROJ_LOGIC</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_INIT</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Applicant details written twice, and the applicant BP now also goes to LOGIN_BP</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_init.
+*CALL METHOD SUPER-&gt;ZIF_RAK_JOURNEY_LOGIC~ON_INIT
+*  EXPORTING
+*    IO_CTX =
+*    .
+    CALL METHOD super-&gt;zif_rak_journey_logic~on_init
+      EXPORTING
+        io_ctx = io_ctx.
+    DATA: lv_loginbp TYPE bu_partner.
+    lv_loginbp       = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_loginbp.
+    DATA(lv_rolebp)  = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_rolebp.
+    DATA(lv_role)    = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_role. "Owner
+    IF lv_loginbp IS NOT INITIAL.
+      NEW zcl_ega_epda_fshry_handler_api( )-&gt;get_bp_details(
+        EXPORTING
+          iv_bp_id      = lv_loginbp
+        IMPORTING
+          es_bp_details = DATA(ls_bp) ).
+      io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).
+      io_ctx-&gt;set_val( iv_name = c_app_bp   iv_value = |{ lv_loginbp }| ).
+*     WRITTEN ONCE. C_PARTNER_NAME is 'APP_NAME' and C_PARTNER_ID is
+*     'APP_ID', and both were then written a SECOND time below this IF, under
+*     a different language rule - so the two disagreed and the later one won.
+*     The pair below the IF was also outside this guard, so a launch with no
+*     login partner blanked the applicant's name and ID rather than leaving
+*     them alone.
+*
+*     The rule kept is the one that degrades: an Arabic session with no
+*     Arabic name on the partner record falls back to the English name
+*     rather than showing an empty applicant.
+      io_ctx-&gt;set_val( iv_name  = c_partner_name
+                       iv_value = COND #( WHEN sy-langu &lt;&gt; c_lang_en AND ls_bp-bp_name_ar IS NOT INITIAL
+                                          THEN CONV string( ls_bp-bp_name_ar )
+                                          ELSE CONV string( ls_bp-bp_name ) ) ).
+      io_ctx-&gt;set_val( iv_name = c_partner_id iv_value = CONV #( ls_bp-emirates_id ) ).
+      io_ctx-&gt;set_val( iv_name = c_partner_mobile iv_value = CONV #( ls_bp-mobile_number ) ).
+      io_ctx-&gt;set_val( iv_name = c_partner_email iv_value = CONV #( ls_bp-email_address ) ).
+      io_ctx-&gt;set_val( iv_name = c_applicanttype iv_value = |{ lv_role }| ).
+    ENDIF.
+  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="150" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>E017</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-687</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_CUSTOM_VALIDATE</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Step 0 refused whenever the role flags disagreed with APPLICANT_ROLE - re-derived now instead of refused</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_custom_validate.
+    rt = super-&gt;zif_rak_journey_logic~on_custom_validate( io_ctx  = io_ctx
+                                                          iv_step = iv_step ).
+    CASE iv_step.
+      WHEN 0.
+*       RE-DERIVED, NOT REFUSED.
+*
+*       PARTNER_OWNER/PARTNER_REP and PERMIT_YES/PERMIT_NO are not answers
+*       in their own right - they are WRITE_FLAGS( )'s projection of
+*       APPLICANT_ROLE and PERMIT_HELD, which are the fields the citizen
+*       actually fills in. This used to refuse the step whenever the role
+*       was set and its flags were not, with "Re-select Owner or
+*       Representative before continuing."
+*
+*       The citizen had already selected it. WRITE_FLAGS( ) only runs from
+*       ON_CHANGE( ), so any round trip that reinstates the model without
+*       raising a change on APPLICANT_ROLE - a backend read answering the
+*       step, the BP search coming back - leaves the role set and the flags
+*       blank. Re-selecting the same value raises no CHANGE either, so the
+*       one instruction the message gave could not clear it: the journey
+*       stopped at step 1. Reported on all three chemical journeys as
+*       "error showing we u select representative and search with owner EID
+*       details, not moving to next step".
+*
+*       Rewriting them is what the handler does at post time anyway -
+*       ON_BEFORE_POST( ) calls WRITE_FLAGS( ) before every post - so doing
+*       it here costs nothing and removes the only state that could block.
+        write_flags( io_ctx ).
+      WHEN 2.
+        DATA(ls_grid) = io_ctx-&gt;get_grid_data( c_grid ).
+        IF ls_grid-rows IS INITIAL.
+          APPEND VALUE #( type  = 'Error' "field = c_grid
+                          text  = `Add at least one chemical row.` ) TO rt.
+        ENDIF.
+      WHEN OTHERS.
+    ENDCASE.
+  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>E017</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-687</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>METHOD VALIDATE_INPUT</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Add Chemical: all fourteen fields enforced. Ten of the checks were commented out</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD validate_input.
+*   ALL FOURTEEN, mirroring the REQUIRED markers in ON_RENDER_POPUP( ).
+*   Ten of these were commented out; CJSMIG-687 Issue 4 settled it.
+    IF io_ctx-&gt;get_val( c_hs_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_mat_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_chem_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_cas_no_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_chem_form_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_packaging_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_quantity_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_gross_weight_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_unit_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_bol_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_exit_port_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_import_pop ) IS INITIAL
+             OR io_ctx-&gt;get_val( c_tport_pop ) IS INITIAL.
+      io_ctx-&gt;add_msg( iv_type = 'Warning'
+                       iv_text = 'Kindly fill required details.' ).
+*     RV_OK stays FALSE. This used to return nothing at all, and ON_POPUP_EVENT
+*     called POPULATE_GRID( ) and CLOSE_POPUP( ) straight afterwards whatever
+*     happened here - so a blank row was added to the grid and the dialog shut,
+*     with only a warning toast to say otherwise. The verdict has to reach the
+*     caller for the message to mean anything.
+      RETURN.
+    ENDIF.
+    rv_ok = abap_true.
+  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>E017</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-687</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_RENDER_POPUP</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Add Chemical: the fourteen required markers, and IV_COLUMNS = 2 for the two-column dialog</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_render_popup.
+    super-&gt;zif_rak_journey_logic~on_render_popup(
+      io_ctx   = io_ctx
+      io_popup = io_popup
+      iv_id    = iv_id
+    ).
+    CASE iv_id.
+*  "On click of ADD Chemical button
+      WHEN c_open_popup.
+*        render_own_popup( io_ctx = io_ctx io_popup = io_popup ).
+*        RETURN.
+*       REQUIRED here is the marker only - DIALOG_FORM( ) sets it on the label
+*       and enforces nothing; a popup's enforcement is the handler's, in
+*       VALIDATE_INPUT( ). So this list has to mirror that method exactly,
+*       and now does: all fourteen marked, all fourteen checked.
+*
+*       That mirror used to read four and four, with ten lines commented out
+*       in VALIDATE_INPUT( ) and a note here saying the decision had not been
+*       made. It has been now - CJSMIG-687 Issue 4, "all fields should be
+*       mandatory" - so both ends were opened together. Change one end and
+*       the other has to move with it, or the dialog either promises an
+*       asterisk it does not enforce or refuses an OK it never marked.
+*
+*       THE HISTORY PICKER IS GONE, not commented out: "Use a previous
+*       declaration - field not required" (same ticket). HISTORY_OPTS( ),
+*       HISTORY_APPLY( ) and C_EVT_HIST are deliberately left in place - the
+*       same ticket asks for the legacy Search-from-History screen, which is
+*       a different control reading the same ChemicalHistorySet, and it will
+*       want them.
+        dialog_form(
+          io_ctx     = io_ctx
+          io_popup   = io_popup
+          iv_title   = 'Add Chemical'
+*         Two per row. "Alignment instead each row one filed, can have 2 or
+*         more field for better user experiences" - fourteen fields one to a
+*         row is a dialog nobody can see the bottom of.
+          iv_columns = 2
+          it_fields  = VALUE #(
+                                ( name = c_hs_pop           label = 'HS Code' required = abap_true
+                                  placeholder = 'e.g. 2933.99.90' )
+                                ( name = c_mat_pop          label = 'Material Name' required = abap_true )
+                                ( name = c_chem_pop         label = 'Chemical Name' required = abap_true )
+                                ( name = c_cas_no_pop       label = 'CAS Number' maxlen = 20 required = abap_true )
+                                ( name = c_chem_form_pop    label = 'Chemical Formula' required = abap_true )
+                                ( name = c_packaging_pop    label = 'Packing' required = abap_true )
+                                ( name = c_quantity_pop     label = 'Quantity' required = abap_true )
+                                ( name = c_gross_weight_pop label = 'Gross Weight' required = abap_true type = 'Number' )
+                                ( name = c_unit_pop         label = 'Unit' required = abap_true
+                                type = 'SELECT'
+                                options = VALUE #( ( key = 'GAL' text = 'Gallon' )
+                                                     ( key = 'KG'  text = 'Kilogram' )
+                                                     ( key = 'LIT' text = 'Liter' )
+                                                     ( key = 'MAT' text = 'Metric Ton' ) ) )
+                                ( name = c_invoice_pop      label = 'Invoice Number' required = abap_true )
+                                ( name = c_import_pop       label = 'Importing Country' shlp = 'H_T005' required = abap_true )
+                                ( name = c_exit_port_pop    label = 'Exit Port' required = abap_true )
+                                ( name = c_bol_pop          label = 'Bill of Lading' required = abap_true )
+                                ( name = c_tport_pop        label = 'Transport Details' required = abap_true )
+                              )
+          iv_ok_text = 'Add'
+          iv_ok_evt  = c_evt_ownok
+          iv_cxl_evt = c_evt_owncx ).
+    ENDCASE.
+  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>E018</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-697</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_CUSTOM_VALIDATE</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Same role-flag fix as E017</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_custom_validate.
+    rt = super-&gt;zif_rak_journey_logic~on_custom_validate( io_ctx  = io_ctx
+                                                          iv_step = iv_step ).
+    CASE iv_step.
+      WHEN 0.
+*       RE-DERIVED, NOT REFUSED.
+*
+*       PARTNER_OWNER/PARTNER_REP and PERMIT_YES/PERMIT_NO are not answers
+*       in their own right - they are WRITE_FLAGS( )'s projection of
+*       APPLICANT_ROLE and PERMIT_HELD, which are the fields the citizen
+*       actually fills in. This used to refuse the step whenever the role
+*       was set and its flags were not, with "Re-select Owner or
+*       Representative before continuing."
+*
+*       The citizen had already selected it. WRITE_FLAGS( ) only runs from
+*       ON_CHANGE( ), so any round trip that reinstates the model without
+*       raising a change on APPLICANT_ROLE - a backend read answering the
+*       step, the BP search coming back - leaves the role set and the flags
+*       blank. Re-selecting the same value raises no CHANGE either, so the
+*       one instruction the message gave could not clear it: the journey
+*       stopped at step 1. Reported on all three chemical journeys as
+*       "error showing we u select representative and search with owner EID
+*       details, not moving to next step".
+*
+*       Rewriting them is what the handler does at post time anyway -
+*       ON_BEFORE_POST( ) calls WRITE_FLAGS( ) before every post - so doing
+*       it here costs nothing and removes the only state that could block.
+        write_flags( io_ctx ).
+      WHEN 2.
+        DATA(ls_grid) = io_ctx-&gt;get_grid_data( c_grid ).
+        IF ls_grid-rows IS INITIAL.
+          APPEND VALUE #( type  = 'Error'
+*                          field = c_grid
+                          text  = `Add at least one material row.` ) TO rt.
+        ENDIF.
+      WHEN OTHERS.
+    ENDCASE.
+  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>E018</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-697</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_RENDER_POPUP</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Add Chemical: the fourteen required markers, and IV_COLUMNS = 2</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_render_popup.
+    super-&gt;zif_rak_journey_logic~on_render_popup(
+          io_ctx   = io_ctx
+          io_popup = io_popup
+          iv_id    = iv_id
+        ).
+**    CHECK iv_id = c_pop_mat.
+    CASE iv_id. "c_chem."
+      WHEN 'c_chem1'.
+*        render_own_popup( io_ctx = io_ctx io_popup = io_popup ).
+*        RETURN.
+      WHEN c_chem. "c_evt_details. "c_chem. "c_evt_details. " FOr F4 use this
+*       REQUIRED here is the marker only - DIALOG_FORM( ) sets it on the label
+*       and enforces nothing; a popup's enforcement is the handler's own, in the
+*       OK event. So this list mirrors WHEN c_evt_ownok exactly - now all
+*       fourteen marked and all fourteen tested, per CJSMIG-697 Issue 4 "all
+*       fields should be mandatory". Move one end and the other has to move
+*       with it.
+        dialog_form(
+          io_ctx     = io_ctx
+          io_popup   = io_popup
+          iv_title   = 'Add Chemical'
+*         Two per row. "Alignment instead each row one filed, can have 2 or
+*         more field for better user experiences" - same ticket.
+          iv_columns = 2
+          it_fields  = VALUE #(
+*                             The history picker stays out: "Use a previous
+*                             declaration - field not required". HISTORY_OPTS( )
+*                             and HISTORY_APPLY( ) are kept for the legacy
+*                             Search-from-History screen the same ticket asks
+*                             for, which is a different control.
+                                ( name = c_hs_code_pop          label = 'HS Code' required = abap_true
+                                  placeholder = 'e.g. 2933.99.90' )
+                                ( name = c_material_name_pop    label = 'Material Name' required = abap_true )
+                                ( name = c_chemical_name_pop    label = 'Chemical Name' required = abap_true )
+                                ( name = c_cas_pop              label = 'CAS Number' maxlen = 20 required = abap_true )
+                                ( name = c_chemical_formula_pop label = 'Chemical Formula' required = abap_true )
+                                ( name = c_packaging_pop        label = 'Packing' required = abap_true )
+                                ( name = c_quantity_pop         label = 'Quantity' required = abap_true )
+                                ( name = c_gross_weight_pop     label = 'Gross Weight' required = abap_true )
+                                ( name = c_uom_pop              label = 'UOM' type = 'SELECT' required = abap_true
+                                  options = VALUE #( ( key = 'GAL' text = 'Gallon' )
+                                                     ( key = 'KG'  text = 'Kilogram' )
+                                                     ( key = 'LIT' text = 'Liter' )
+                                                     ( key = 'MAT' text = 'Metric Ton' ) ) )
+                                ( name = c_invoice_pop          label = 'Invoice Number' required = abap_true )
+                                ( name = c_origin_pop           label = 'Country of Origin' shlp = 'H_T005' required = abap_true )
+                                ( name = c_end_user_pop         label = 'Point of Entrance' required = abap_true )
+                                ( name = c_bol_pop              label = 'Bill of Lading' required = abap_true )
+                                ( name = c_trans_comp           label = 'Transport Company' required = abap_true )
+                              )
+          iv_ok_text = 'Add'
+          iv_ok_evt  = c_evt_ownok
+          iv_cxl_evt = c_evt_owncx ).
+        RETURN.
+*        dialog_form(
+*          io_ctx     = io_ctx
+*          io_popup   = io_popup
+*          iv_title   = 'Add Chemical'
+*          it_fields  = VALUE #(
+*                                ( name = c_hs_code_pop          label = 'HS Code'  )
+*                                ( name = c_material_name_pop    label = 'Material Name' )
+*                                ( name = c_chemical_name_pop    label = 'Chemical Name' )
+*                                ( name = c_cas_pop              label = 'CAS Number' )
+*                                ( name = c_chemical_formula_pop label = 'Chemical Formula' )
+*                                ( name = c_packaging_pop        label = 'Packing' )
+*                                ( name = c_quantity_pop         label = 'Quantity'  )
+*                                ( name = c_gross_weight_pop     label = 'Gross Weight'  )
+*                                ( name = c_uom_pop              label = 'UOM'  )
+*                                ( name = c_invoice_pop          label = 'Invoice Number'  )
+*                                ( name = c_origin_pop           label = 'Country of Origin'  )
+*                                ( name = c_end_user_pop         label = 'Point of Entrance'  )
+*                                ( name = c_bol_pop              label = 'Bill of Lading'  )
+*                                ( name = c_trans_comp           label = 'Transport Company'  )
+*                              )
+*          iv_ok_text = 'Add'
+*          iv_ok_evt  = c_own_add ).
+      WHEN OTHERS.
+    ENDCASE.
+  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>E018</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-697</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_POPUP_EVENT</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Add Chemical: all fourteen enforced on OK, and the dialog stays open when one fails</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_popup_event.
+    CALL METHOD super-&gt;zif_rak_journey_logic~on_popup_event
+      EXPORTING
+        io_ctx   = io_ctx
+        iv_id    = iv_id
+        iv_event = iv_event.
+    CASE iv_event.
+      WHEN c_evt_details.
+        chem_form_load( io_ctx ).          " no id = a new owner
+        io_ctx-&gt;open_popup( c_chem ).
+      WHEN c_evt_ownok. "'OWNER_ADD'. "
+*       Nothing here used to check any field - Add saved whatever was typed,
+*       blank fields included. All fourteen are now tested, mirroring the
+*       REQUIRED markers in ON_RENDER_POPUP( ) one for one.
+        IF io_ctx-&gt;get_val( c_hs_code_pop )          IS INITIAL
+           OR io_ctx-&gt;get_val( c_material_name_pop )    IS INITIAL
+           OR io_ctx-&gt;get_val( c_chemical_name_pop )    IS INITIAL
+           OR io_ctx-&gt;get_val( c_cas_pop )              IS INITIAL
+           OR io_ctx-&gt;get_val( c_chemical_formula_pop ) IS INITIAL
+           OR io_ctx-&gt;get_val( c_packaging_pop )     IS INITIAL
+           OR io_ctx-&gt;get_val( c_quantity_pop )      IS INITIAL
+           OR io_ctx-&gt;get_val( c_gross_weight_pop )  IS INITIAL
+           OR io_ctx-&gt;get_val( c_uom_pop )           IS INITIAL
+           OR io_ctx-&gt;get_val( c_invoice_pop )       IS INITIAL
+           OR io_ctx-&gt;get_val( c_origin_pop )        IS INITIAL
+           OR io_ctx-&gt;get_val( c_end_user_pop )      IS INITIAL
+           OR io_ctx-&gt;get_val( c_bol_pop )           IS INITIAL
+           OR io_ctx-&gt;get_val( c_trans_comp )        IS INITIAL.
+          io_ctx-&gt;add_msg( iv_type = 'Warning'
+                           iv_text = 'Kindly fill required details.' ).
+          RETURN.
+        ENDIF.
+        own_form_save( io_ctx ).
+        io_ctx-&gt;close_popup( ). "Close pop-up screen after adding data
+*      WHEN c_evt_hist.
+**       Fill the dialog from the chosen declaration and leave it OPEN - this
+**       shipment's own figures are still to type.
+*        history_apply( io_ctx ).
+      WHEN c_evt_owncx. "'CANCEL'. "
+        io_ctx-&gt;close_popup( ).
+*      WHEN c_evt_ownsr.
+*        own_search( io_ctx ).
+      WHEN OTHERS.
+*    "Edit Chemicals Details GRID
+        IF iv_event CP c_edit_pop.
+          own_edit( io_ctx = io_ctx iv_id = substring( val = iv_event off = 9 ) ).
+          io_ctx-&gt;open_popup( c_chem ).
+          RETURN.
+*     "Delete data from Chemicals Details GRID
+        ELSEIF iv_event CP c_DELETE_POP.
+          own_delete( io_ctx = io_ctx iv_id = substring( val = iv_event off = 8 ) ).
+          RETURN.
+        ENDIF.
+    ENDCASE.
+  ENDMETHOD.</t>
         </is>
       </c>
     </row>

--- a/doc/tickets/CJS_journey_ownership.xlsx
+++ b/doc/tickets/CJS_journey_ownership.xlsx
@@ -6778,7 +6778,7 @@
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>The class had no active version at all - a CONSTANTS ... TYPE string VALUE '' will not compile - so SAP was running an older build of every method on this journey. Fixed in git. Pull, activate, and re-test this line first.</t>
+          <t>The class had no active version at all - a CONSTANTS ... TYPE string VALUE '' will not compile - so SAP was running an older build of every method on this journey. The one-line correction is on the Handler code sheet. Fix it, activate, and re-test this line first.</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Applicant details written twice, and the applicant BP now also goes to LOGIN_BP</t>
+          <t>Applicant details were written twice on ON_INIT</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -9564,7 +9564,6 @@
         IMPORTING
           es_bp_details = DATA(ls_bp) ).
       io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).
-      io_ctx-&gt;set_val( iv_name = c_app_bp   iv_value = |{ lv_loginbp }| ).
 *     WRITTEN ONCE. C_PARTNER_NAME is 'APP_NAME' and C_PARTNER_ID is
 *     'APP_ID', and both were then written a SECOND time below this IF, under
 *     a different language rule - so the two disagreed and the later one won.
@@ -9591,30 +9590,71 @@
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>E022 E026 E027 D021 D014gv</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>CJSMIG-684 / 704</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>six classes - see the code</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>see the code</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>The applicant's own partner never reached LOGIN_BP, the field every other journey and the record model use. Additive: the existing OWNER_BP write is left alone, so nothing that works today changes</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>* Applies to ZCL_EPDA_E022_DEV_PROJ_LOGIC, ZCL_E026_TREE_REMOVAL_LOGIC,
+* ZCL_E027_VICE_CAPTAIN_LOGIC, ZCL_D021_MOD_SCHOOL_FEE_LOGIC and
+* ZCL_D014_STAFF_GOLD_VISA_LOGIC - all five declare C_LOGIN_BP as 'OWNER_BP'.
+* E025 is the exception and has its own row above: there OWNER_BP is the owner
+* SEARCH box, so the constant itself has to be corrected, not added to.
+* --- private section: ADD this. Leave C_LOGIN_BP exactly as it is. ----
+  constants C_APP_BP type STRING value 'LOGIN_BP' ##NO_TEXT.
+* --- ON_INIT: ADD the second line under the existing first one. -------
+    io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).
+    io_ctx-&gt;set_val( iv_name = c_app_bp   iv_value = |{ lv_loginbp }| ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="150" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>E017</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>CJSMIG-687</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_CUSTOM_VALIDATE</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Step 0 refused whenever the role flags disagreed with APPLICANT_ROLE - re-derived now instead of refused</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_custom_validate.
     rt = super-&gt;zif_rak_journey_logic~on_custom_validate( io_ctx  = io_ctx
@@ -9656,33 +9696,33 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>E017</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>CJSMIG-687</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>METHOD VALIDATE_INPUT</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Add Chemical: all fourteen fields enforced. Ten of the checks were commented out</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  METHOD validate_input.
 *   ALL FOURTEEN, mirroring the REQUIRED markers in ON_RENDER_POPUP( ).
@@ -9714,33 +9754,33 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12" ht="150" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>E017</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>CJSMIG-687</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_RENDER_POPUP</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Add Chemical: the fourteen required markers, and IV_COLUMNS = 2 for the two-column dialog</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_render_popup.
     super-&gt;zif_rak_journey_logic~on_render_popup(
@@ -9809,33 +9849,33 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13" ht="150" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>E018</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>CJSMIG-697</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_CUSTOM_VALIDATE</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Same role-flag fix as E017</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_custom_validate.
     rt = super-&gt;zif_rak_journey_logic~on_custom_validate( io_ctx  = io_ctx
@@ -9878,33 +9918,33 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14" ht="150" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>E018</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>CJSMIG-697</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_RENDER_POPUP</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Add Chemical: the fourteen required markers, and IV_COLUMNS = 2</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_render_popup.
     super-&gt;zif_rak_journey_logic~on_render_popup(
@@ -9989,33 +10029,33 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>E018</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>CJSMIG-697</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_POPUP_EVENT</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Add Chemical: all fourteen enforced on OK, and the dialog stays open when one fails</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_popup_event.
     CALL METHOD super-&gt;zif_rak_journey_logic~on_popup_event

--- a/doc/tickets/CJS_journey_ownership.xlsx
+++ b/doc/tickets/CJS_journey_ownership.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,19 @@
       <name val="Consolas"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +119,11 @@
         <fgColor rgb="00F6DDE1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EEED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -126,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,7 +197,11 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -9350,15 +9370,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:A459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="120" customWidth="1" min="6" max="6"/>
+    <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9369,749 +9384,2903 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>These are the journey's OWN class, not the framework. Read it, take it or write your own - it is your service. Where a whole method is given, it is the complete current method: replace the method body with it. Nothing here is pushed for you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Journey</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Ticket</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Method / where</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>What it fixes</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>E025</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-703</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E025_BEEKEEPING_LOGIC</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>see the code</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Applicant BP was written to the owner SEARCH field and then blanked</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>* --- private section: the constant named the wrong field ------------
-*   was:  constants C_LOGIN_BP type STRING value 'OWNER_BP' ##NO_TEXT.
-  constants C_LOGIN_BP type STRING value 'LOGIN_BP' ##NO_TEXT.
-* --- ZIF_RAK_JOURNEY_LOGIC~ON_INIT, last line inside the IF -----------
-*   was:  io_ctx-&gt;set_val( iv_name = 'OWNER_BP' iv_value = ' ' ).
-*   'OWNER_BP' is the owner search box (see ON_SEARCH), not the applicant.
-  io_ctx-&gt;set_val( iv_name = c_owner_bp iv_value = ' ' ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>E026</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-704</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E026_TREE_REMOVAL_LOGIC</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>see the code</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Applicant BP never reached LOGIN_BP</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>* --- private section: add, leave C_LOGIN_BP exactly as it is ---------
-  constants C_APP_BP type STRING value 'LOGIN_BP' ##NO_TEXT.
-* --- ZIF_RAK_JOURNEY_LOGIC~ON_INIT, straight after the existing line --
-    io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).
-    io_ctx-&gt;set_val( iv_name = c_app_bp   iv_value = |{ lv_loginbp }| ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>E018</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-697</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>see the code</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>The class had NO ACTIVE VERSION - a string constant does not take an empty literal, so every earlier fix was in the source and none of it was running</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>* --- private section --------------------------------------------------
-*   was:  constants C_IMPEXP type STRING value ''.       &lt;- will not compile
-  constants C_IMPEXP type STRING value IS INITIAL ##NO_TEXT.
-* Activate the class after this and re-test the whole journey - including the
-* CX_SY_CONVERSION_NO_NUMBER on post, which may go with it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="150" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>E022</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-684</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_EPDA_E022_DEV_PROJ_LOGIC</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_INIT</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Applicant details were written twice on ON_INIT</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_init.
-*CALL METHOD SUPER-&gt;ZIF_RAK_JOURNEY_LOGIC~ON_INIT
-*  EXPORTING
-*    IO_CTX =
-*    .
-    CALL METHOD super-&gt;zif_rak_journey_logic~on_init
-      EXPORTING
-        io_ctx = io_ctx.
-    DATA: lv_loginbp TYPE bu_partner.
-    lv_loginbp       = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_loginbp.
-    DATA(lv_rolebp)  = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_rolebp.
-    DATA(lv_role)    = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_role. "Owner
-    IF lv_loginbp IS NOT INITIAL.
-      NEW zcl_ega_epda_fshry_handler_api( )-&gt;get_bp_details(
-        EXPORTING
-          iv_bp_id      = lv_loginbp
-        IMPORTING
-          es_bp_details = DATA(ls_bp) ).
-      io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).
-*     WRITTEN ONCE. C_PARTNER_NAME is 'APP_NAME' and C_PARTNER_ID is
-*     'APP_ID', and both were then written a SECOND time below this IF, under
-*     a different language rule - so the two disagreed and the later one won.
-*     The pair below the IF was also outside this guard, so a launch with no
-*     login partner blanked the applicant's name and ID rather than leaving
-*     them alone.
-*
-*     The rule kept is the one that degrades: an Arabic session with no
-*     Arabic name on the partner record falls back to the English name
-*     rather than showing an empty applicant.
-      io_ctx-&gt;set_val( iv_name  = c_partner_name
-                       iv_value = COND #( WHEN sy-langu &lt;&gt; c_lang_en AND ls_bp-bp_name_ar IS NOT INITIAL
-                                          THEN CONV string( ls_bp-bp_name_ar )
-                                          ELSE CONV string( ls_bp-bp_name ) ) ).
-      io_ctx-&gt;set_val( iv_name = c_partner_id iv_value = CONV #( ls_bp-emirates_id ) ).
-      io_ctx-&gt;set_val( iv_name = c_partner_mobile iv_value = CONV #( ls_bp-mobile_number ) ).
-      io_ctx-&gt;set_val( iv_name = c_partner_email iv_value = CONV #( ls_bp-email_address ) ).
-      io_ctx-&gt;set_val( iv_name = c_applicanttype iv_value = |{ lv_role }| ).
-    ENDIF.
-  ENDMETHOD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="150" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>E022 E026 E027 D021 D014gv</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-684 / 704</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>six classes - see the code</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>see the code</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>The applicant's own partner never reached LOGIN_BP, the field every other journey and the record model use. Additive: the existing OWNER_BP write is left alone, so nothing that works today changes</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>* Applies to ZCL_EPDA_E022_DEV_PROJ_LOGIC, ZCL_E026_TREE_REMOVAL_LOGIC,
-* ZCL_E027_VICE_CAPTAIN_LOGIC, ZCL_D021_MOD_SCHOOL_FEE_LOGIC and
-* ZCL_D014_STAFF_GOLD_VISA_LOGIC - all five declare C_LOGIN_BP as 'OWNER_BP'.
-* E025 is the exception and has its own row above: there OWNER_BP is the owner
-* SEARCH box, so the constant itself has to be corrected, not added to.
-* --- private section: ADD this. Leave C_LOGIN_BP exactly as it is. ----
-  constants C_APP_BP type STRING value 'LOGIN_BP' ##NO_TEXT.
-* --- ON_INIT: ADD the second line under the existing first one. -------
-    io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).
-    io_ctx-&gt;set_val( iv_name = c_app_bp   iv_value = |{ lv_loginbp }| ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>E017</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-687</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_CUSTOM_VALIDATE</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Step 0 refused whenever the role flags disagreed with APPLICANT_ROLE - re-derived now instead of refused</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_custom_validate.
-    rt = super-&gt;zif_rak_journey_logic~on_custom_validate( io_ctx  = io_ctx
-                                                          iv_step = iv_step ).
-    CASE iv_step.
-      WHEN 0.
-*       RE-DERIVED, NOT REFUSED.
-*
-*       PARTNER_OWNER/PARTNER_REP and PERMIT_YES/PERMIT_NO are not answers
-*       in their own right - they are WRITE_FLAGS( )'s projection of
-*       APPLICANT_ROLE and PERMIT_HELD, which are the fields the citizen
-*       actually fills in. This used to refuse the step whenever the role
-*       was set and its flags were not, with "Re-select Owner or
-*       Representative before continuing."
-*
-*       The citizen had already selected it. WRITE_FLAGS( ) only runs from
-*       ON_CHANGE( ), so any round trip that reinstates the model without
-*       raising a change on APPLICANT_ROLE - a backend read answering the
-*       step, the BP search coming back - leaves the role set and the flags
-*       blank. Re-selecting the same value raises no CHANGE either, so the
-*       one instruction the message gave could not clear it: the journey
-*       stopped at step 1. Reported on all three chemical journeys as
-*       "error showing we u select representative and search with owner EID
-*       details, not moving to next step".
-*
-*       Rewriting them is what the handler does at post time anyway -
-*       ON_BEFORE_POST( ) calls WRITE_FLAGS( ) before every post - so doing
-*       it here costs nothing and removes the only state that could block.
-        write_flags( io_ctx ).
-      WHEN 2.
-        DATA(ls_grid) = io_ctx-&gt;get_grid_data( c_grid ).
-        IF ls_grid-rows IS INITIAL.
-          APPEND VALUE #( type  = 'Error' "field = c_grid
-                          text  = `Add at least one chemical row.` ) TO rt.
-        ENDIF.
-      WHEN OTHERS.
-    ENDCASE.
-  ENDMETHOD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>E017</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-687</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>METHOD VALIDATE_INPUT</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Add Chemical: all fourteen fields enforced. Ten of the checks were commented out</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  METHOD validate_input.
-*   ALL FOURTEEN, mirroring the REQUIRED markers in ON_RENDER_POPUP( ).
-*   Ten of these were commented out; CJSMIG-687 Issue 4 settled it.
-    IF io_ctx-&gt;get_val( c_hs_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_mat_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_chem_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_cas_no_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_chem_form_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_packaging_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_quantity_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_gross_weight_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_unit_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_bol_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_exit_port_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_import_pop ) IS INITIAL
-             OR io_ctx-&gt;get_val( c_tport_pop ) IS INITIAL.
-      io_ctx-&gt;add_msg( iv_type = 'Warning'
-                       iv_text = 'Kindly fill required details.' ).
-*     RV_OK stays FALSE. This used to return nothing at all, and ON_POPUP_EVENT
-*     called POPULATE_GRID( ) and CLOSE_POPUP( ) straight afterwards whatever
-*     happened here - so a blank row was added to the grid and the dialog shut,
-*     with only a warning toast to say otherwise. The verdict has to reach the
-*     caller for the message to mean anything.
-      RETURN.
-    ENDIF.
-    rv_ok = abap_true.
-  ENDMETHOD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>E017</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-687</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_RENDER_POPUP</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Add Chemical: the fourteen required markers, and IV_COLUMNS = 2 for the two-column dialog</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_render_popup.
-    super-&gt;zif_rak_journey_logic~on_render_popup(
-      io_ctx   = io_ctx
-      io_popup = io_popup
-      iv_id    = iv_id
-    ).
-    CASE iv_id.
-*  "On click of ADD Chemical button
-      WHEN c_open_popup.
-*        render_own_popup( io_ctx = io_ctx io_popup = io_popup ).
-*        RETURN.
-*       REQUIRED here is the marker only - DIALOG_FORM( ) sets it on the label
-*       and enforces nothing; a popup's enforcement is the handler's, in
-*       VALIDATE_INPUT( ). So this list has to mirror that method exactly,
-*       and now does: all fourteen marked, all fourteen checked.
-*
-*       That mirror used to read four and four, with ten lines commented out
-*       in VALIDATE_INPUT( ) and a note here saying the decision had not been
-*       made. It has been now - CJSMIG-687 Issue 4, "all fields should be
-*       mandatory" - so both ends were opened together. Change one end and
-*       the other has to move with it, or the dialog either promises an
-*       asterisk it does not enforce or refuses an OK it never marked.
-*
-*       THE HISTORY PICKER IS GONE, not commented out: "Use a previous
-*       declaration - field not required" (same ticket). HISTORY_OPTS( ),
-*       HISTORY_APPLY( ) and C_EVT_HIST are deliberately left in place - the
-*       same ticket asks for the legacy Search-from-History screen, which is
-*       a different control reading the same ChemicalHistorySet, and it will
-*       want them.
-        dialog_form(
-          io_ctx     = io_ctx
-          io_popup   = io_popup
-          iv_title   = 'Add Chemical'
-*         Two per row. "Alignment instead each row one filed, can have 2 or
-*         more field for better user experiences" - fourteen fields one to a
-*         row is a dialog nobody can see the bottom of.
-          iv_columns = 2
-          it_fields  = VALUE #(
-                                ( name = c_hs_pop           label = 'HS Code' required = abap_true
-                                  placeholder = 'e.g. 2933.99.90' )
-                                ( name = c_mat_pop          label = 'Material Name' required = abap_true )
-                                ( name = c_chem_pop         label = 'Chemical Name' required = abap_true )
-                                ( name = c_cas_no_pop       label = 'CAS Number' maxlen = 20 required = abap_true )
-                                ( name = c_chem_form_pop    label = 'Chemical Formula' required = abap_true )
-                                ( name = c_packaging_pop    label = 'Packing' required = abap_true )
-                                ( name = c_quantity_pop     label = 'Quantity' required = abap_true )
-                                ( name = c_gross_weight_pop label = 'Gross Weight' required = abap_true type = 'Number' )
-                                ( name = c_unit_pop         label = 'Unit' required = abap_true
-                                type = 'SELECT'
-                                options = VALUE #( ( key = 'GAL' text = 'Gallon' )
-                                                     ( key = 'KG'  text = 'Kilogram' )
-                                                     ( key = 'LIT' text = 'Liter' )
-                                                     ( key = 'MAT' text = 'Metric Ton' ) ) )
-                                ( name = c_invoice_pop      label = 'Invoice Number' required = abap_true )
-                                ( name = c_import_pop       label = 'Importing Country' shlp = 'H_T005' required = abap_true )
-                                ( name = c_exit_port_pop    label = 'Exit Port' required = abap_true )
-                                ( name = c_bol_pop          label = 'Bill of Lading' required = abap_true )
-                                ( name = c_tport_pop        label = 'Transport Details' required = abap_true )
-                              )
-          iv_ok_text = 'Add'
-          iv_ok_evt  = c_evt_ownok
-          iv_cxl_evt = c_evt_owncx ).
-    ENDCASE.
-  ENDMETHOD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>E018</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-697</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_CUSTOM_VALIDATE</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Same role-flag fix as E017</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_custom_validate.
-    rt = super-&gt;zif_rak_journey_logic~on_custom_validate( io_ctx  = io_ctx
-                                                          iv_step = iv_step ).
-    CASE iv_step.
-      WHEN 0.
-*       RE-DERIVED, NOT REFUSED.
-*
-*       PARTNER_OWNER/PARTNER_REP and PERMIT_YES/PERMIT_NO are not answers
-*       in their own right - they are WRITE_FLAGS( )'s projection of
-*       APPLICANT_ROLE and PERMIT_HELD, which are the fields the citizen
-*       actually fills in. This used to refuse the step whenever the role
-*       was set and its flags were not, with "Re-select Owner or
-*       Representative before continuing."
-*
-*       The citizen had already selected it. WRITE_FLAGS( ) only runs from
-*       ON_CHANGE( ), so any round trip that reinstates the model without
-*       raising a change on APPLICANT_ROLE - a backend read answering the
-*       step, the BP search coming back - leaves the role set and the flags
-*       blank. Re-selecting the same value raises no CHANGE either, so the
-*       one instruction the message gave could not clear it: the journey
-*       stopped at step 1. Reported on all three chemical journeys as
-*       "error showing we u select representative and search with owner EID
-*       details, not moving to next step".
-*
-*       Rewriting them is what the handler does at post time anyway -
-*       ON_BEFORE_POST( ) calls WRITE_FLAGS( ) before every post - so doing
-*       it here costs nothing and removes the only state that could block.
-        write_flags( io_ctx ).
-      WHEN 2.
-        DATA(ls_grid) = io_ctx-&gt;get_grid_data( c_grid ).
-        IF ls_grid-rows IS INITIAL.
-          APPEND VALUE #( type  = 'Error'
-*                          field = c_grid
-                          text  = `Add at least one material row.` ) TO rt.
-        ENDIF.
-      WHEN OTHERS.
-    ENDCASE.
-  ENDMETHOD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>E018</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-697</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_RENDER_POPUP</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Add Chemical: the fourteen required markers, and IV_COLUMNS = 2</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_render_popup.
-    super-&gt;zif_rak_journey_logic~on_render_popup(
-          io_ctx   = io_ctx
-          io_popup = io_popup
-          iv_id    = iv_id
-        ).
-**    CHECK iv_id = c_pop_mat.
-    CASE iv_id. "c_chem."
-      WHEN 'c_chem1'.
-*        render_own_popup( io_ctx = io_ctx io_popup = io_popup ).
-*        RETURN.
-      WHEN c_chem. "c_evt_details. "c_chem. "c_evt_details. " FOr F4 use this
-*       REQUIRED here is the marker only - DIALOG_FORM( ) sets it on the label
-*       and enforces nothing; a popup's enforcement is the handler's own, in the
-*       OK event. So this list mirrors WHEN c_evt_ownok exactly - now all
-*       fourteen marked and all fourteen tested, per CJSMIG-697 Issue 4 "all
-*       fields should be mandatory". Move one end and the other has to move
-*       with it.
-        dialog_form(
-          io_ctx     = io_ctx
-          io_popup   = io_popup
-          iv_title   = 'Add Chemical'
-*         Two per row. "Alignment instead each row one filed, can have 2 or
-*         more field for better user experiences" - same ticket.
-          iv_columns = 2
-          it_fields  = VALUE #(
-*                             The history picker stays out: "Use a previous
-*                             declaration - field not required". HISTORY_OPTS( )
-*                             and HISTORY_APPLY( ) are kept for the legacy
-*                             Search-from-History screen the same ticket asks
-*                             for, which is a different control.
-                                ( name = c_hs_code_pop          label = 'HS Code' required = abap_true
-                                  placeholder = 'e.g. 2933.99.90' )
-                                ( name = c_material_name_pop    label = 'Material Name' required = abap_true )
-                                ( name = c_chemical_name_pop    label = 'Chemical Name' required = abap_true )
-                                ( name = c_cas_pop              label = 'CAS Number' maxlen = 20 required = abap_true )
-                                ( name = c_chemical_formula_pop label = 'Chemical Formula' required = abap_true )
-                                ( name = c_packaging_pop        label = 'Packing' required = abap_true )
-                                ( name = c_quantity_pop         label = 'Quantity' required = abap_true )
-                                ( name = c_gross_weight_pop     label = 'Gross Weight' required = abap_true )
-                                ( name = c_uom_pop              label = 'UOM' type = 'SELECT' required = abap_true
-                                  options = VALUE #( ( key = 'GAL' text = 'Gallon' )
-                                                     ( key = 'KG'  text = 'Kilogram' )
-                                                     ( key = 'LIT' text = 'Liter' )
-                                                     ( key = 'MAT' text = 'Metric Ton' ) ) )
-                                ( name = c_invoice_pop          label = 'Invoice Number' required = abap_true )
-                                ( name = c_origin_pop           label = 'Country of Origin' shlp = 'H_T005' required = abap_true )
-                                ( name = c_end_user_pop         label = 'Point of Entrance' required = abap_true )
-                                ( name = c_bol_pop              label = 'Bill of Lading' required = abap_true )
-                                ( name = c_trans_comp           label = 'Transport Company' required = abap_true )
-                              )
-          iv_ok_text = 'Add'
-          iv_ok_evt  = c_evt_ownok
-          iv_cxl_evt = c_evt_owncx ).
-        RETURN.
-*        dialog_form(
-*          io_ctx     = io_ctx
-*          io_popup   = io_popup
-*          iv_title   = 'Add Chemical'
-*          it_fields  = VALUE #(
-*                                ( name = c_hs_code_pop          label = 'HS Code'  )
-*                                ( name = c_material_name_pop    label = 'Material Name' )
-*                                ( name = c_chemical_name_pop    label = 'Chemical Name' )
-*                                ( name = c_cas_pop              label = 'CAS Number' )
-*                                ( name = c_chemical_formula_pop label = 'Chemical Formula' )
-*                                ( name = c_packaging_pop        label = 'Packing' )
-*                                ( name = c_quantity_pop         label = 'Quantity'  )
-*                                ( name = c_gross_weight_pop     label = 'Gross Weight'  )
-*                                ( name = c_uom_pop              label = 'UOM'  )
-*                                ( name = c_invoice_pop          label = 'Invoice Number'  )
-*                                ( name = c_origin_pop           label = 'Country of Origin'  )
-*                                ( name = c_end_user_pop         label = 'Point of Entrance'  )
-*                                ( name = c_bol_pop              label = 'Bill of Lading'  )
-*                                ( name = c_trans_comp           label = 'Transport Company'  )
-*                              )
-*          iv_ok_text = 'Add'
-*          iv_ok_evt  = c_own_add ).
-      WHEN OTHERS.
-    ENDCASE.
-  ENDMETHOD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>E018</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>CJSMIG-697</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_POPUP_EVENT</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Add Chemical: all fourteen enforced on OK, and the dialog stays open when one fails</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_popup_event.
-    CALL METHOD super-&gt;zif_rak_journey_logic~on_popup_event
-      EXPORTING
-        io_ctx   = io_ctx
-        iv_id    = iv_id
-        iv_event = iv_event.
-    CASE iv_event.
-      WHEN c_evt_details.
-        chem_form_load( io_ctx ).          " no id = a new owner
-        io_ctx-&gt;open_popup( c_chem ).
-      WHEN c_evt_ownok. "'OWNER_ADD'. "
-*       Nothing here used to check any field - Add saved whatever was typed,
-*       blank fields included. All fourteen are now tested, mirroring the
-*       REQUIRED markers in ON_RENDER_POPUP( ) one for one.
-        IF io_ctx-&gt;get_val( c_hs_code_pop )          IS INITIAL
-           OR io_ctx-&gt;get_val( c_material_name_pop )    IS INITIAL
-           OR io_ctx-&gt;get_val( c_chemical_name_pop )    IS INITIAL
-           OR io_ctx-&gt;get_val( c_cas_pop )              IS INITIAL
-           OR io_ctx-&gt;get_val( c_chemical_formula_pop ) IS INITIAL
-           OR io_ctx-&gt;get_val( c_packaging_pop )     IS INITIAL
-           OR io_ctx-&gt;get_val( c_quantity_pop )      IS INITIAL
-           OR io_ctx-&gt;get_val( c_gross_weight_pop )  IS INITIAL
-           OR io_ctx-&gt;get_val( c_uom_pop )           IS INITIAL
-           OR io_ctx-&gt;get_val( c_invoice_pop )       IS INITIAL
-           OR io_ctx-&gt;get_val( c_origin_pop )        IS INITIAL
-           OR io_ctx-&gt;get_val( c_end_user_pop )      IS INITIAL
-           OR io_ctx-&gt;get_val( c_bol_pop )           IS INITIAL
-           OR io_ctx-&gt;get_val( c_trans_comp )        IS INITIAL.
-          io_ctx-&gt;add_msg( iv_type = 'Warning'
-                           iv_text = 'Kindly fill required details.' ).
-          RETURN.
-        ENDIF.
-        own_form_save( io_ctx ).
-        io_ctx-&gt;close_popup( ). "Close pop-up screen after adding data
-*      WHEN c_evt_hist.
-**       Fill the dialog from the chosen declaration and leave it OPEN - this
-**       shipment's own figures are still to type.
-*        history_apply( io_ctx ).
-      WHEN c_evt_owncx. "'CANCEL'. "
-        io_ctx-&gt;close_popup( ).
-*      WHEN c_evt_ownsr.
-*        own_search( io_ctx ).
-      WHEN OTHERS.
-*    "Edit Chemicals Details GRID
-        IF iv_event CP c_edit_pop.
-          own_edit( io_ctx = io_ctx iv_id = substring( val = iv_event off = 9 ) ).
-          io_ctx-&gt;open_popup( c_chem ).
-          RETURN.
-*     "Delete data from Chemicals Details GRID
-        ELSEIF iv_event CP c_DELETE_POP.
-          own_delete( io_ctx = io_ctx iv_id = substring( val = iv_event off = 8 ) ).
-          RETURN.
-        ENDIF.
-    ENDCASE.
-  ENDMETHOD.</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The journey's OWN class, not the framework. Read it, take it, or write your own - it is your service. Where a whole method is given it is the complete current method: replace the method body with it. Nothing here is pushed for anyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>E025  ·  CJSMIG-703  ·  ZCL_E025_BEEKEEPING_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>see the code below   |   Applicant BP was written to the owner SEARCH field and then blanked</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>* --- private section: the constant named the wrong field ------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>*   was:  constants C_LOGIN_BP type STRING value 'OWNER_BP' ##NO_TEXT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  constants C_LOGIN_BP type STRING value 'LOGIN_BP' ##NO_TEXT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>* --- ZIF_RAK_JOURNEY_LOGIC~ON_INIT, last line inside the IF -----------</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>*   was:  io_ctx-&gt;set_val( iv_name = 'OWNER_BP' iv_value = ' ' ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>*   'OWNER_BP' is the owner search box (see ON_SEARCH), not the applicant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  io_ctx-&gt;set_val( iv_name = c_owner_bp iv_value = ' ' ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>E026  ·  CJSMIG-704  ·  ZCL_E026_TREE_REMOVAL_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>see the code below   |   Applicant BP never reached LOGIN_BP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>* --- private section: add, leave C_LOGIN_BP exactly as it is ---------</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  constants C_APP_BP type STRING value 'LOGIN_BP' ##NO_TEXT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>* --- ZIF_RAK_JOURNEY_LOGIC~ON_INIT, straight after the existing line --</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    io_ctx-&gt;set_val( iv_name = c_app_bp   iv_value = |{ lv_loginbp }| ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>E018  ·  CJSMIG-697  ·  ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>see the code below   |   The class had NO ACTIVE VERSION - a string constant does not take an empty literal, so every earlier fix was in the source and none of it was running</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>* --- private section --------------------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>*   was:  constants C_IMPEXP type STRING value ''.       &lt;- will not compile</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  constants C_IMPEXP type STRING value IS INITIAL ##NO_TEXT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>* Activate the class after this and re-test the whole journey - including the</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>* CX_SY_CONVERSION_NO_NUMBER on post, which may go with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>E022  ·  CJSMIG-684  ·  ZCL_EPDA_E022_DEV_PROJ_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_INIT   |   Applicant details were written twice on ON_INIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>*CALL METHOD SUPER-&gt;ZIF_RAK_JOURNEY_LOGIC~ON_INIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>*  EXPORTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>*    IO_CTX =</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>*    .</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CALL METHOD super-&gt;zif_rak_journey_logic~on_init</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      EXPORTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        io_ctx = io_ctx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DATA: lv_loginbp TYPE bu_partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    lv_loginbp       = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_loginbp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DATA(lv_rolebp)  = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_rolebp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    DATA(lv_role)    = CAST zcl_rak_journey_engine( io_ctx )-&gt;mv_role. "Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    IF lv_loginbp IS NOT INITIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      NEW zcl_ega_epda_fshry_handler_api( )-&gt;get_bp_details(</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        EXPORTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_bp_id      = lv_loginbp</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IMPORTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          es_bp_details = DATA(ls_bp) ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>*     WRITTEN ONCE. C_PARTNER_NAME is 'APP_NAME' and C_PARTNER_ID is</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>*     'APP_ID', and both were then written a SECOND time below this IF, under</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>*     a different language rule - so the two disagreed and the later one won.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>*     The pair below the IF was also outside this guard, so a launch with no</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>*     login partner blanked the applicant's name and ID rather than leaving</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>*     them alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>*     The rule kept is the one that degrades: an Arabic session with no</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>*     Arabic name on the partner record falls back to the English name</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>*     rather than showing an empty applicant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_ctx-&gt;set_val( iv_name  = c_partner_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       iv_value = COND #( WHEN sy-langu &lt;&gt; c_lang_en AND ls_bp-bp_name_ar IS NOT INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                          THEN CONV string( ls_bp-bp_name_ar )</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                          ELSE CONV string( ls_bp-bp_name ) ) ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="22" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_ctx-&gt;set_val( iv_name = c_partner_id iv_value = CONV #( ls_bp-emirates_id ) ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="22" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_ctx-&gt;set_val( iv_name = c_partner_mobile iv_value = CONV #( ls_bp-mobile_number ) ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_ctx-&gt;set_val( iv_name = c_partner_email iv_value = CONV #( ls_bp-email_address ) ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="22" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_ctx-&gt;set_val( iv_name = c_applicanttype iv_value = |{ lv_role }| ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="22" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ENDIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="22" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="20" t="inlineStr">
+        <is>
+          <t>E022 E026 E027 D021 D014gv  ·  CJSMIG-684 / 704  ·  six classes - see the code</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>see the code below   |   The applicant's own partner never reached LOGIN_BP, the field every other journey and the record model use. Additive: the existing OWNER_BP write is left alone, so nothing that works today changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>* Applies to ZCL_EPDA_E022_DEV_PROJ_LOGIC, ZCL_E026_TREE_REMOVAL_LOGIC,</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>* ZCL_E027_VICE_CAPTAIN_LOGIC, ZCL_D021_MOD_SCHOOL_FEE_LOGIC and</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>* ZCL_D014_STAFF_GOLD_VISA_LOGIC - all five declare C_LOGIN_BP as 'OWNER_BP'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>* E025 is the exception and has its own row above: there OWNER_BP is the owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="22" t="inlineStr">
+        <is>
+          <t>* SEARCH box, so the constant itself has to be corrected, not added to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="22" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="22" t="inlineStr">
+        <is>
+          <t>* --- private section: ADD this. Leave C_LOGIN_BP exactly as it is. ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  constants C_APP_BP type STRING value 'LOGIN_BP' ##NO_TEXT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="22" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="22" t="inlineStr">
+        <is>
+          <t>* --- ON_INIT: ADD the second line under the existing first one. -------</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    io_ctx-&gt;set_val( iv_name = c_login_bp iv_value = |{ lv_loginbp }| ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    io_ctx-&gt;set_val( iv_name = c_app_bp   iv_value = |{ lv_loginbp }| ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>E017  ·  CJSMIG-687  ·  ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_CUSTOM_VALIDATE   |   Step 0 refused whenever the role flags disagreed with APPLICANT_ROLE - re-derived now instead of refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_custom_validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="22" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rt = super-&gt;zif_rak_journey_logic~on_custom_validate( io_ctx  = io_ctx</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                          iv_step = iv_step ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="22" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CASE iv_step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="22" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>*       RE-DERIVED, NOT REFUSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>*       PARTNER_OWNER/PARTNER_REP and PERMIT_YES/PERMIT_NO are not answers</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>*       in their own right - they are WRITE_FLAGS( )'s projection of</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>*       APPLICANT_ROLE and PERMIT_HELD, which are the fields the citizen</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="22" t="inlineStr">
+        <is>
+          <t>*       actually fills in. This used to refuse the step whenever the role</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>*       was set and its flags were not, with "Re-select Owner or</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="22" t="inlineStr">
+        <is>
+          <t>*       Representative before continuing."</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="22" t="inlineStr">
+        <is>
+          <t>*       The citizen had already selected it. WRITE_FLAGS( ) only runs from</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="22" t="inlineStr">
+        <is>
+          <t>*       ON_CHANGE( ), so any round trip that reinstates the model without</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="22" t="inlineStr">
+        <is>
+          <t>*       raising a change on APPLICANT_ROLE - a backend read answering the</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="22" t="inlineStr">
+        <is>
+          <t>*       step, the BP search coming back - leaves the role set and the flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="22" t="inlineStr">
+        <is>
+          <t>*       blank. Re-selecting the same value raises no CHANGE either, so the</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>*       one instruction the message gave could not clear it: the journey</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="22" t="inlineStr">
+        <is>
+          <t>*       stopped at step 1. Reported on all three chemical journeys as</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="22" t="inlineStr">
+        <is>
+          <t>*       "error showing we u select representative and search with owner EID</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="22" t="inlineStr">
+        <is>
+          <t>*       details, not moving to next step".</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="22" t="inlineStr">
+        <is>
+          <t>*       Rewriting them is what the handler does at post time anyway -</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="22" t="inlineStr">
+        <is>
+          <t>*       ON_BEFORE_POST( ) calls WRITE_FLAGS( ) before every post - so doing</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="22" t="inlineStr">
+        <is>
+          <t>*       it here costs nothing and removes the only state that could block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        write_flags( io_ctx ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="22" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        DATA(ls_grid) = io_ctx-&gt;get_grid_data( c_grid ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IF ls_grid-rows IS INITIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          APPEND VALUE #( type  = 'Error' "field = c_grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                          text  = `Add at least one chemical row.` ) TO rt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ENDIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="22" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN OTHERS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ENDCASE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="22" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="20" t="inlineStr">
+        <is>
+          <t>E017  ·  CJSMIG-687  ·  ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="30" customHeight="1">
+      <c r="A151" s="21" t="inlineStr">
+        <is>
+          <t>METHOD VALIDATE_INPUT   |   Add Chemical: all fourteen fields enforced. Ten of the checks were commented out</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD validate_input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="22" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="22" t="inlineStr">
+        <is>
+          <t>*   ALL FOURTEEN, mirroring the REQUIRED markers in ON_RENDER_POPUP( ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="22" t="inlineStr">
+        <is>
+          <t>*   Ten of these were commented out; CJSMIG-687 Issue 4 settled it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    IF io_ctx-&gt;get_val( c_hs_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_mat_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_chem_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_cas_no_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_chem_form_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_packaging_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_quantity_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_gross_weight_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_unit_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_bol_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_exit_port_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_import_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             OR io_ctx-&gt;get_val( c_tport_pop ) IS INITIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="22" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="22" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_ctx-&gt;add_msg( iv_type = 'Warning'</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                       iv_text = 'Kindly fill required details.' ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="22" t="inlineStr">
+        <is>
+          <t>*     RV_OK stays FALSE. This used to return nothing at all, and ON_POPUP_EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>*     called POPULATE_GRID( ) and CLOSE_POPUP( ) straight afterwards whatever</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="22" t="inlineStr">
+        <is>
+          <t>*     happened here - so a blank row was added to the grid and the dialog shut,</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>*     with only a warning toast to say otherwise. The verdict has to reach the</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="22" t="inlineStr">
+        <is>
+          <t>*     caller for the message to mean anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      RETURN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ENDIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="22" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rv_ok = abap_true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="22" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="20" t="inlineStr">
+        <is>
+          <t>E017  ·  CJSMIG-687  ·  ZCL_E017_NOC_EXP_CHEM_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="30" customHeight="1">
+      <c r="A186" s="21" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_RENDER_POPUP   |   Add Chemical: the fourteen required markers, and IV_COLUMNS = 2 for the two-column dialog</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_render_popup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    super-&gt;zif_rak_journey_logic~on_render_popup(</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_ctx   = io_ctx</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      io_popup = io_popup</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      iv_id    = iv_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="22" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CASE iv_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="22" t="inlineStr">
+        <is>
+          <t>*  "On click of ADD Chemical button</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN c_open_popup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="22" t="inlineStr">
+        <is>
+          <t>*        render_own_popup( io_ctx = io_ctx io_popup = io_popup ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="22" t="inlineStr">
+        <is>
+          <t>*        RETURN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="22" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="22" t="inlineStr">
+        <is>
+          <t>*       REQUIRED here is the marker only - DIALOG_FORM( ) sets it on the label</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="22" t="inlineStr">
+        <is>
+          <t>*       and enforces nothing; a popup's enforcement is the handler's, in</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="22" t="inlineStr">
+        <is>
+          <t>*       VALIDATE_INPUT( ). So this list has to mirror that method exactly,</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="22" t="inlineStr">
+        <is>
+          <t>*       and now does: all fourteen marked, all fourteen checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="22" t="inlineStr">
+        <is>
+          <t>*       That mirror used to read four and four, with ten lines commented out</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="22" t="inlineStr">
+        <is>
+          <t>*       in VALIDATE_INPUT( ) and a note here saying the decision had not been</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="22" t="inlineStr">
+        <is>
+          <t>*       made. It has been now - CJSMIG-687 Issue 4, "all fields should be</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="22" t="inlineStr">
+        <is>
+          <t>*       mandatory" - so both ends were opened together. Change one end and</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="22" t="inlineStr">
+        <is>
+          <t>*       the other has to move with it, or the dialog either promises an</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="22" t="inlineStr">
+        <is>
+          <t>*       asterisk it does not enforce or refuses an OK it never marked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="22" t="inlineStr">
+        <is>
+          <t>*       THE HISTORY PICKER IS GONE, not commented out: "Use a previous</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="22" t="inlineStr">
+        <is>
+          <t>*       declaration - field not required" (same ticket). HISTORY_OPTS( ),</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="22" t="inlineStr">
+        <is>
+          <t>*       HISTORY_APPLY( ) and C_EVT_HIST are deliberately left in place - the</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="22" t="inlineStr">
+        <is>
+          <t>*       same ticket asks for the legacy Search-from-History screen, which is</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="22" t="inlineStr">
+        <is>
+          <t>*       a different control reading the same ChemicalHistorySet, and it will</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="22" t="inlineStr">
+        <is>
+          <t>*       want them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        dialog_form(</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          io_ctx     = io_ctx</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          io_popup   = io_popup</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_title   = 'Add Chemical'</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="22" t="inlineStr">
+        <is>
+          <t>*         Two per row. "Alignment instead each row one filed, can have 2 or</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="22" t="inlineStr">
+        <is>
+          <t>*         more field for better user experiences" - fourteen fields one to a</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="22" t="inlineStr">
+        <is>
+          <t>*         row is a dialog nobody can see the bottom of.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_columns = 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          it_fields  = VALUE #(</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_hs_pop           label = 'HS Code' required = abap_true</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  placeholder = 'e.g. 2933.99.90' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_mat_pop          label = 'Material Name' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_chem_pop         label = 'Chemical Name' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_cas_no_pop       label = 'CAS Number' maxlen = 20 required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_chem_form_pop    label = 'Chemical Formula' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_packaging_pop    label = 'Packing' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_quantity_pop     label = 'Quantity' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_gross_weight_pop label = 'Gross Weight' required = abap_true type = 'Number' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_unit_pop         label = 'Unit' required = abap_true</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                type = 'SELECT'</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                options = VALUE #( ( key = 'GAL' text = 'Gallon' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                     ( key = 'KG'  text = 'Kilogram' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                     ( key = 'LIT' text = 'Liter' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                     ( key = 'MAT' text = 'Metric Ton' ) ) )</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_invoice_pop      label = 'Invoice Number' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_import_pop       label = 'Importing Country' shlp = 'H_T005' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_exit_port_pop    label = 'Exit Port' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_bol_pop          label = 'Bill of Lading' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_tport_pop        label = 'Transport Details' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              )</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_ok_text = 'Add'</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_ok_evt  = c_evt_ownok</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_cxl_evt = c_evt_owncx ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ENDCASE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="20" t="inlineStr">
+        <is>
+          <t>E018  ·  CJSMIG-697  ·  ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="30" customHeight="1">
+      <c r="A255" s="21" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_CUSTOM_VALIDATE   |   Same role-flag fix as E017</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_custom_validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    rt = super-&gt;zif_rak_journey_logic~on_custom_validate( io_ctx  = io_ctx</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                          iv_step = iv_step ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="22" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CASE iv_step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="22" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="22" t="inlineStr">
+        <is>
+          <t>*       RE-DERIVED, NOT REFUSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="22" t="inlineStr">
+        <is>
+          <t>*       PARTNER_OWNER/PARTNER_REP and PERMIT_YES/PERMIT_NO are not answers</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="22" t="inlineStr">
+        <is>
+          <t>*       in their own right - they are WRITE_FLAGS( )'s projection of</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="22" t="inlineStr">
+        <is>
+          <t>*       APPLICANT_ROLE and PERMIT_HELD, which are the fields the citizen</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="22" t="inlineStr">
+        <is>
+          <t>*       actually fills in. This used to refuse the step whenever the role</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="22" t="inlineStr">
+        <is>
+          <t>*       was set and its flags were not, with "Re-select Owner or</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="22" t="inlineStr">
+        <is>
+          <t>*       Representative before continuing."</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="22" t="inlineStr">
+        <is>
+          <t>*       The citizen had already selected it. WRITE_FLAGS( ) only runs from</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="22" t="inlineStr">
+        <is>
+          <t>*       ON_CHANGE( ), so any round trip that reinstates the model without</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="22" t="inlineStr">
+        <is>
+          <t>*       raising a change on APPLICANT_ROLE - a backend read answering the</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="22" t="inlineStr">
+        <is>
+          <t>*       step, the BP search coming back - leaves the role set and the flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="22" t="inlineStr">
+        <is>
+          <t>*       blank. Re-selecting the same value raises no CHANGE either, so the</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="22" t="inlineStr">
+        <is>
+          <t>*       one instruction the message gave could not clear it: the journey</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="22" t="inlineStr">
+        <is>
+          <t>*       stopped at step 1. Reported on all three chemical journeys as</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="22" t="inlineStr">
+        <is>
+          <t>*       "error showing we u select representative and search with owner EID</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="22" t="inlineStr">
+        <is>
+          <t>*       details, not moving to next step".</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="22" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="22" t="inlineStr">
+        <is>
+          <t>*       Rewriting them is what the handler does at post time anyway -</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="22" t="inlineStr">
+        <is>
+          <t>*       ON_BEFORE_POST( ) calls WRITE_FLAGS( ) before every post - so doing</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="22" t="inlineStr">
+        <is>
+          <t>*       it here costs nothing and removes the only state that could block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        write_flags( io_ctx ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="22" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        DATA(ls_grid) = io_ctx-&gt;get_grid_data( c_grid ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IF ls_grid-rows IS INITIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          APPEND VALUE #( type  = 'Error'</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="22" t="inlineStr">
+        <is>
+          <t>*                          field = c_grid</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                          text  = `Add at least one material row.` ) TO rt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ENDIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="22" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN OTHERS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ENDCASE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="22" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="20" customHeight="1">
+      <c r="A300" s="20" t="inlineStr">
+        <is>
+          <t>E018  ·  CJSMIG-697  ·  ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="30" customHeight="1">
+      <c r="A301" s="21" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_RENDER_POPUP   |   Add Chemical: the fourteen required markers, and IV_COLUMNS = 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_render_popup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="22" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    super-&gt;zif_rak_journey_logic~on_render_popup(</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          io_ctx   = io_ctx</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          io_popup = io_popup</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_id    = iv_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="22" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="22" t="inlineStr">
+        <is>
+          <t>**    CHECK iv_id = c_pop_mat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CASE iv_id. "c_chem."</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN 'c_chem1'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="22" t="inlineStr">
+        <is>
+          <t>*        render_own_popup( io_ctx = io_ctx io_popup = io_popup ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="22" t="inlineStr">
+        <is>
+          <t>*        RETURN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN c_chem. "c_evt_details. "c_chem. "c_evt_details. " FOr F4 use this</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="22" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="22" t="inlineStr">
+        <is>
+          <t>*       REQUIRED here is the marker only - DIALOG_FORM( ) sets it on the label</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="22" t="inlineStr">
+        <is>
+          <t>*       and enforces nothing; a popup's enforcement is the handler's own, in the</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="22" t="inlineStr">
+        <is>
+          <t>*       OK event. So this list mirrors WHEN c_evt_ownok exactly - now all</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="22" t="inlineStr">
+        <is>
+          <t>*       fourteen marked and all fourteen tested, per CJSMIG-697 Issue 4 "all</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="22" t="inlineStr">
+        <is>
+          <t>*       fields should be mandatory". Move one end and the other has to move</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="22" t="inlineStr">
+        <is>
+          <t>*       with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        dialog_form(</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          io_ctx     = io_ctx</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          io_popup   = io_popup</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_title   = 'Add Chemical'</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="22" t="inlineStr">
+        <is>
+          <t>*         Two per row. "Alignment instead each row one filed, can have 2 or</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="22" t="inlineStr">
+        <is>
+          <t>*         more field for better user experiences" - same ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_columns = 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          it_fields  = VALUE #(</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="22" t="inlineStr">
+        <is>
+          <t>*                             The history picker stays out: "Use a previous</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="22" t="inlineStr">
+        <is>
+          <t>*                             declaration - field not required". HISTORY_OPTS( )</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="22" t="inlineStr">
+        <is>
+          <t>*                             and HISTORY_APPLY( ) are kept for the legacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="22" t="inlineStr">
+        <is>
+          <t>*                             Search-from-History screen the same ticket asks</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="22" t="inlineStr">
+        <is>
+          <t>*                             for, which is a different control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_hs_code_pop          label = 'HS Code' required = abap_true</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  placeholder = 'e.g. 2933.99.90' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_material_name_pop    label = 'Material Name' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_chemical_name_pop    label = 'Chemical Name' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_cas_pop              label = 'CAS Number' maxlen = 20 required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_chemical_formula_pop label = 'Chemical Formula' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_packaging_pop        label = 'Packing' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_quantity_pop         label = 'Quantity' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_gross_weight_pop     label = 'Gross Weight' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_uom_pop              label = 'UOM' type = 'SELECT' required = abap_true</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  options = VALUE #( ( key = 'GAL' text = 'Gallon' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                     ( key = 'KG'  text = 'Kilogram' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                     ( key = 'LIT' text = 'Liter' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                     ( key = 'MAT' text = 'Metric Ton' ) ) )</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="22" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_invoice_pop          label = 'Invoice Number' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_origin_pop           label = 'Country of Origin' shlp = 'H_T005' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_end_user_pop         label = 'Point of Entrance' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_bol_pop              label = 'Bill of Lading' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                ( name = c_trans_comp           label = 'Transport Company' required = abap_true )</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              )</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="22" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_ok_text = 'Add'</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_ok_evt  = c_evt_ownok</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          iv_cxl_evt = c_evt_owncx ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        RETURN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="22" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="22" t="inlineStr">
+        <is>
+          <t>*        dialog_form(</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="22" t="inlineStr">
+        <is>
+          <t>*          io_ctx     = io_ctx</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="22" t="inlineStr">
+        <is>
+          <t>*          io_popup   = io_popup</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="22" t="inlineStr">
+        <is>
+          <t>*          iv_title   = 'Add Chemical'</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="22" t="inlineStr">
+        <is>
+          <t>*          it_fields  = VALUE #(</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_hs_code_pop          label = 'HS Code'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_material_name_pop    label = 'Material Name' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_chemical_name_pop    label = 'Chemical Name' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_cas_pop              label = 'CAS Number' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_chemical_formula_pop label = 'Chemical Formula' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_packaging_pop        label = 'Packing' )</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_quantity_pop         label = 'Quantity'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_gross_weight_pop     label = 'Gross Weight'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_uom_pop              label = 'UOM'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_invoice_pop          label = 'Invoice Number'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_origin_pop           label = 'Country of Origin'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_end_user_pop         label = 'Point of Entrance'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_bol_pop              label = 'Bill of Lading'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="22" t="inlineStr">
+        <is>
+          <t>*                                ( name = c_trans_comp           label = 'Transport Company'  )</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="22" t="inlineStr">
+        <is>
+          <t>*                              )</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="22" t="inlineStr">
+        <is>
+          <t>*          iv_ok_text = 'Add'</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="22" t="inlineStr">
+        <is>
+          <t>*          iv_ok_evt  = c_own_add ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="22" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN OTHERS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ENDCASE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="22" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ENDMETHOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="20" customHeight="1">
+      <c r="A391" s="20" t="inlineStr">
+        <is>
+          <t>E018  ·  CJSMIG-697  ·  ZCL_E018_NOC_TRANS_CHEM_LOGIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="30" customHeight="1">
+      <c r="A392" s="21" t="inlineStr">
+        <is>
+          <t>METHOD ZIF_RAK_JOURNEY_LOGIC~ON_POPUP_EVENT   |   Add Chemical: all fourteen enforced on OK, and the dialog stays open when one fails</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  METHOD zif_rak_journey_logic~on_popup_event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="22" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="22" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="22" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CALL METHOD super-&gt;zif_rak_journey_logic~on_popup_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      EXPORTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        io_ctx   = io_ctx</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        iv_id    = iv_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        iv_event = iv_event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="22" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CASE iv_event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN c_evt_details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chem_form_load( io_ctx ).          " no id = a new owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        io_ctx-&gt;open_popup( c_chem ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="22" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN c_evt_ownok. "'OWNER_ADD'. "</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="22" t="inlineStr">
+        <is>
+          <t>*       Nothing here used to check any field - Add saved whatever was typed,</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="22" t="inlineStr">
+        <is>
+          <t>*       blank fields included. All fourteen are now tested, mirroring the</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="22" t="inlineStr">
+        <is>
+          <t>*       REQUIRED markers in ON_RENDER_POPUP( ) one for one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IF io_ctx-&gt;get_val( c_hs_code_pop )          IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_material_name_pop )    IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_chemical_name_pop )    IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_cas_pop )              IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_chemical_formula_pop ) IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_packaging_pop )     IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_quantity_pop )      IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_gross_weight_pop )  IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_uom_pop )           IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_invoice_pop )       IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_origin_pop )        IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_end_user_pop )      IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_bol_pop )           IS INITIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           OR io_ctx-&gt;get_val( c_trans_comp )        IS INITIAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          io_ctx-&gt;add_msg( iv_type = 'Warning'</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                           iv_text = 'Kindly fill required details.' ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          RETURN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ENDIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="22" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        own_form_save( io_ctx ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        io_ctx-&gt;close_popup( ). "Close pop-up screen after adding data</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="22" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="22" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="22" t="inlineStr">
+        <is>
+          <t>*      WHEN c_evt_hist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="22" t="inlineStr">
+        <is>
+          <t>**       Fill the dialog from the chosen declaration and leave it OPEN - this</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="22" t="inlineStr">
+        <is>
+          <t>**       shipment's own figures are still to type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="22" t="inlineStr">
+        <is>
+          <t>*        history_apply( io_ctx ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="22" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN c_evt_owncx. "'CANCEL'. "</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        io_ctx-&gt;close_popup( ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="22" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="22" t="inlineStr">
+        <is>
+          <t>*      WHEN c_evt_ownsr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="22" t="inlineStr">
+        <is>
+          <t>*        own_search( io_ctx ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="22" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      WHEN OTHERS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="22" t="inlineStr">
+        <is>
+          <t>*    "Edit Chemicals Details GRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        IF iv_event CP c_edit_pop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          own_edit( io_ctx = io_ctx iv_id = substring( val = iv_event off = 9 ) ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          io_ctx-&gt;open_popup( c_chem ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          RETURN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="22" t="inlineStr">
+        <is>
+          <t>*     "Delete data from Chemicals Details GRID</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ELSEIF iv_event CP c_DELETE_POP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          own_delete( io_ctx = io_ctx iv_id = substring( val = iv_event off = 8 ) ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          RETURN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        ENDIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="22" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ENDCASE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ENDMETHOD.</t>
         </is>
       </c>
     </row>
